--- a/src/test/resources/campaigncreation.xlsx
+++ b/src/test/resources/campaigncreation.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9270"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="create" sheetId="1" r:id="rId1"/>
+    <sheet name="edit" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>campaign name</t>
   </si>
@@ -90,9 +91,6 @@
   </si>
   <si>
     <t>Location type</t>
-  </si>
-  <si>
-    <t>MyLocation</t>
   </si>
   <si>
     <r>
@@ -120,6 +118,18 @@
   </si>
   <si>
     <t>FestiveSale</t>
+  </si>
+  <si>
+    <t>telangana</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Share Venue Contact Info </t>
+  </si>
+  <si>
+    <t>Online</t>
   </si>
 </sst>
 </file>
@@ -169,12 +179,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,7 +524,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N1" t="s">
         <v>19</v>
@@ -524,10 +535,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -554,10 +565,10 @@
         <v>9</v>
       </c>
       <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
         <v>24</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
       </c>
       <c r="M2" t="s">
         <v>16</v>
@@ -601,7 +612,10 @@
         <v>9</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
       </c>
       <c r="M3" t="s">
         <v>17</v>
@@ -648,4 +662,51 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="32.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/campaigncreation.xlsx
+++ b/src/test/resources/campaigncreation.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9270" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9270"/>
   </bookViews>
   <sheets>
     <sheet name="create" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>campaign name</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>Mart</t>
   </si>
   <si>
     <t xml:space="preserve">MediKit </t>
@@ -130,6 +127,18 @@
   </si>
   <si>
     <t>Online</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>Medical</t>
   </si>
 </sst>
 </file>
@@ -494,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
         <v>5</v>
@@ -518,16 +527,16 @@
         <v>4</v>
       </c>
       <c r="K1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L1" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O1" t="s">
         <v>11</v>
@@ -535,25 +544,25 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>2026</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>2026</v>
@@ -565,33 +574,33 @@
         <v>9</v>
       </c>
       <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
       <c r="M2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
       </c>
       <c r="E3">
         <v>2026</v>
@@ -600,7 +609,7 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3">
         <v>2026</v>
@@ -609,30 +618,99 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
         <v>17</v>
       </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
       <c r="O3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>2026</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4">
+        <v>2026</v>
+      </c>
+      <c r="I4">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>2026</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5">
+        <v>2026</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -681,22 +759,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
         <v>28</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
       </c>
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">

--- a/src/test/resources/campaigncreation.xlsx
+++ b/src/test/resources/campaigncreation.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
   <si>
     <t>campaign name</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t xml:space="preserve">MediKit </t>
-  </si>
-  <si>
-    <t>January</t>
   </si>
   <si>
     <t>Time Bounds</t>
@@ -503,7 +500,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
         <v>5</v>
@@ -527,16 +524,16 @@
         <v>4</v>
       </c>
       <c r="K1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L1" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O1" t="s">
         <v>11</v>
@@ -544,16 +541,16 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>2026</v>
@@ -562,7 +559,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H2">
         <v>2026</v>
@@ -574,19 +571,19 @@
         <v>9</v>
       </c>
       <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -594,13 +591,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>2026</v>
@@ -609,7 +606,7 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H3">
         <v>2026</v>
@@ -618,30 +615,30 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
         <v>16</v>
       </c>
-      <c r="N3" t="s">
-        <v>17</v>
-      </c>
       <c r="O3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>2026</v>
@@ -650,7 +647,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4">
         <v>2026</v>
@@ -659,30 +656,30 @@
         <v>20</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s">
         <v>16</v>
-      </c>
-      <c r="N4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>2026</v>
@@ -691,7 +688,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5">
         <v>2026</v>
@@ -700,16 +697,16 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -759,10 +756,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="M1" s="3"/>
     </row>
@@ -771,10 +768,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
